--- a/costos/Estimacion_Costos_Medical_Health.xlsx
+++ b/costos/Estimacion_Costos_Medical_Health.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencias" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Azure'!$A$3:$K$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AWS'!$A$3:$K$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Azure'!$A$3:$L$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AWS'!$A$3:$L$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,13 +25,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00####"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.000"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -185,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,16 +192,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,6 +216,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -238,6 +239,9 @@
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -256,16 +260,20 @@
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -369,7 +377,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Costo mensual por categoría (USD)</a:t>
+              <a:t>Costo mensual por categoría (COP)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -458,7 +466,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>USD / mes</a:t>
+                  <a:t>COP / mes</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -484,7 +492,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -794,7 +802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -816,7 +824,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comparación mensual por categoría (USD, pago por uso). Precios de lista consultados en Octubre 2026.</t>
+          <t>Comparación mensual por categoría en pesos colombianos (COP), pago por uso. Precios de lista en USD consultados en Octubre 2026 y convertidos con la TRM de la hoja Supuestos.</t>
         </is>
       </c>
     </row>
@@ -828,12 +836,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Azure (mensual)</t>
+          <t>Azure (COP/mes)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AWS (mensual)</t>
+          <t>AWS (COP/mes)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -848,12 +856,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Azure (anual)</t>
+          <t>Azure (COP/año)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>AWS (anual)</t>
+          <t>AWS (COP/año)</t>
         </is>
       </c>
     </row>
@@ -864,11 +872,11 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A5,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A5,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A5,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A5,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D5" s="5">
@@ -895,11 +903,11 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A6,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A6,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A6,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A6,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D6" s="5">
@@ -926,11 +934,11 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A7,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A7,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A7,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A7,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D7" s="5">
@@ -957,11 +965,11 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A8,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A8,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C8" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A8,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A8,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D8" s="5">
@@ -988,11 +996,11 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A9,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A9,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C9" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A9,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A9,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D9" s="5">
@@ -1019,11 +1027,11 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A10,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A10,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C10" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A10,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A10,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D10" s="5">
@@ -1050,11 +1058,11 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,$A11,Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,$A11,Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>SUMIF(AWS!$A$4:$A$55,$A11,AWS!$I$4:$I$55)</f>
+        <f>SUMIF(AWS!$A$4:$A$55,$A11,AWS!$J$4:$J$55)</f>
         <v/>
       </c>
       <c r="D11" s="5">
@@ -1115,7 +1123,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Costo mensual Azure (pago por uso)</t>
+          <t>Costo mensual Azure en COP (pago por uso)</t>
         </is>
       </c>
       <c r="B15" s="11">
@@ -1126,7 +1134,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Costo mensual Azure con optimizaciones</t>
+          <t>Costo mensual Azure en COP con reservas a 1 año</t>
         </is>
       </c>
       <c r="B16" s="11">
@@ -1137,7 +1145,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Costo por enfermera al mes (Azure optimizado)</t>
+          <t>Costo por enfermera al mes en COP (reservas a 1 año)</t>
         </is>
       </c>
       <c r="B17" s="11">
@@ -1148,10 +1156,10 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Costo por llamada atendida (Azure optimizado)</t>
-        </is>
-      </c>
-      <c r="B18" s="12">
+          <t>Costo por llamada atendida en COP (reservas a 1 año)</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
         <f>Optimización!$C$14/Supuestos!$B$8</f>
         <v/>
       </c>
@@ -1159,10 +1167,10 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Costo anual Azure con optimizaciones</t>
-        </is>
-      </c>
-      <c r="B19" s="13">
+          <t>Costo anual Azure en COP con reservas a 1 año</t>
+        </is>
+      </c>
+      <c r="B19" s="11">
         <f>Optimización!$C$14*12</f>
         <v/>
       </c>
@@ -1170,10 +1178,10 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Costo total a 3 años (TCO) Azure con reservas a 3 años</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
+          <t>Costo total a 3 años (TCO) en COP con reservas a 3 años</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
         <f>Optimización!$D$14*36</f>
         <v/>
       </c>
@@ -1181,10 +1189,21 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>Costo mensual Azure en USD (referencia)</t>
+        </is>
+      </c>
+      <c r="B21" s="12">
+        <f>Azure!$I$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Diferencia AWS vs Azure (pago por uso)</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B22" s="13">
         <f>(C12-B12)/B12</f>
         <v/>
       </c>
@@ -1201,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1252,7 +1271,7 @@
           <t>Horas por mes</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="14" t="n">
         <v>730</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1272,7 +1291,7 @@
           <t>Días por mes</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="14" t="n">
         <v>30.42</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1292,7 +1311,7 @@
           <t>Enfermeras</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="14" t="n">
         <v>250</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1312,7 +1331,7 @@
           <t>Supervisoras y administradores</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1332,7 +1351,7 @@
           <t>Llamadas atendidas por mes</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="14" t="n">
         <v>180000</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1352,7 +1371,7 @@
           <t>Tasa de remisión a centro médico</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="15" t="n">
         <v>0.2</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1372,7 +1391,7 @@
           <t>Remisiones por mes</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <f>B8*B9</f>
         <v/>
       </c>
@@ -1393,7 +1412,7 @@
           <t>Peticiones API por llamada</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="14" t="n">
         <v>80</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1413,7 +1432,7 @@
           <t>Peticiones API por mes</t>
         </is>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <f>B8*B11</f>
         <v/>
       </c>
@@ -1434,7 +1453,7 @@
           <t>Tokens de entrada por triaje</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="14" t="n">
         <v>2000</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1454,7 +1473,7 @@
           <t>Tokens de salida por triaje</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1474,7 +1493,7 @@
           <t>Peticiones FHIR por llamada</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1494,7 +1513,7 @@
           <t>Almacenamiento clínico FHIR</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="14" t="n">
         <v>200</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1514,7 +1533,7 @@
           <t>Almacenamiento de documentos (Blob/S3)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="14" t="n">
         <v>1024</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1534,7 +1553,7 @@
           <t>Almacenamiento PostgreSQL aprovisionado</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="14" t="n">
         <v>512</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1554,7 +1573,7 @@
           <t>Logs ingeridos por mes</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="14" t="n">
         <v>200</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1574,7 +1593,7 @@
           <t>Salida de datos a internet</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1594,7 +1613,7 @@
           <t>Remisiones con llamada de voz</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1614,7 +1633,7 @@
           <t>Minutos por llamada de voz</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1634,7 +1653,7 @@
           <t>Muestras Prometheus por mes</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="14" t="n">
         <v>1500</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1654,7 +1673,7 @@
           <t>Transferencia entre regiones</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="14" t="n">
         <v>300</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1674,7 +1693,7 @@
           <t>Nodos Kubernetes región primaria (promedio)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n">
+      <c r="B25" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1694,7 +1713,7 @@
           <t>Nodos Kubernetes región secundaria</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1714,7 +1733,7 @@
           <t>vCPU por nodo</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1725,6 +1744,26 @@
       <c r="D27" s="4" t="inlineStr">
         <is>
           <t>D4s v5 / m6i.xlarge: 4 vCPU, 16 GB RAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TRM (pesos colombianos por dólar)</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>3273.49</v>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Banco de la República, vigente del 3 al 5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1751,8 +1790,9 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1817,262 +1857,287 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Costo anual (USD)</t>
+          <t>Costo mensual (COP)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>Costo anual (COP)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>Referencia</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Azure Kubernetes Service</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Plano de control Standard (SLA 99,95%)</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>East US 2 + Central US</t>
         </is>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>clúster-hora</t>
         </is>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="20">
         <f>E4*G4*H4</f>
         <v/>
       </c>
       <c r="J4" s="21">
-        <f>I4*12</f>
-        <v/>
-      </c>
-      <c r="K4" s="22" t="inlineStr">
+        <f>I4*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>J4*12</f>
+        <v/>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/kubernetes-service/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>AKS - nodos región primaria</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Standard_D4s_v5 Linux (4 vCPU, 16 GB)</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <f>Supuestos!$B$25</f>
         <v/>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.192</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="20">
         <f>E5*G5*H5</f>
         <v/>
       </c>
       <c r="J5" s="21">
-        <f>I5*12</f>
-        <v/>
-      </c>
-      <c r="K5" s="22" t="inlineStr">
+        <f>I5*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>J5*12</f>
+        <v/>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/virtual-machines/linux/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>AKS - nodos región secundaria</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Standard_D4s_v5 Linux (4 vCPU, 16 GB)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Central US</t>
         </is>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <f>Supuestos!$B$26</f>
         <v/>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>0.192</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <f>E6*G6*H6</f>
         <v/>
       </c>
       <c r="J6" s="21">
-        <f>I6*12</f>
-        <v/>
-      </c>
-      <c r="K6" s="22" t="inlineStr">
+        <f>I6*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>J6*12</f>
+        <v/>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/virtual-machines/linux/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Discos de SO de los nodos</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Premium SSD P10 (128 GB)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <f>Supuestos!$B$25+Supuestos!$B$26</f>
         <v/>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>disco-mes</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>17.92</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="20">
         <f>E7*G7*H7</f>
         <v/>
       </c>
       <c r="J7" s="21">
-        <f>I7*12</f>
-        <v/>
-      </c>
-      <c r="K7" s="22" t="inlineStr">
+        <f>I7*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>J7*12</f>
+        <v/>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/managed-disks/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Azure Container Registry</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Premium + 1 réplica geográfica</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>East US 2 + Central US</t>
         </is>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>registro-día</t>
         </is>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="18">
         <f>Supuestos!$B$5</f>
         <v/>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="19" t="n">
         <v>1.6666</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="20">
         <f>E8*G8*H8</f>
         <v/>
       </c>
       <c r="J8" s="21">
-        <f>I8*12</f>
-        <v/>
-      </c>
-      <c r="K8" s="22" t="inlineStr">
+        <f>I8*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>J8*12</f>
+        <v/>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/container-registry/</t>
         </is>
@@ -2118,11 +2183,15 @@
         <f>E9*G9*H9</f>
         <v/>
       </c>
-      <c r="J9" s="27">
-        <f>I9*12</f>
-        <v/>
-      </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="J9" s="28">
+        <f>I9*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="28">
+        <f>J9*12</f>
+        <v/>
+      </c>
+      <c r="L9" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/postgresql/flexible-server/</t>
         </is>
@@ -2168,11 +2237,15 @@
         <f>E10*G10*H10</f>
         <v/>
       </c>
-      <c r="J10" s="27">
-        <f>I10*12</f>
-        <v/>
-      </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="J10" s="28">
+        <f>I10*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K10" s="28">
+        <f>J10*12</f>
+        <v/>
+      </c>
+      <c r="L10" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/postgresql/flexible-server/</t>
         </is>
@@ -2218,11 +2291,15 @@
         <f>E11*G11*H11</f>
         <v/>
       </c>
-      <c r="J11" s="27">
-        <f>I11*12</f>
-        <v/>
-      </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="J11" s="28">
+        <f>I11*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K11" s="28">
+        <f>J11*12</f>
+        <v/>
+      </c>
+      <c r="L11" s="29" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/postgresql/flexible-server/concepts-read-replicas</t>
         </is>
@@ -2268,11 +2345,15 @@
         <f>E12*G12*H12</f>
         <v/>
       </c>
-      <c r="J12" s="27">
-        <f>I12*12</f>
-        <v/>
-      </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="J12" s="28">
+        <f>I12*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K12" s="28">
+        <f>J12*12</f>
+        <v/>
+      </c>
+      <c r="L12" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/postgresql/flexible-server/</t>
         </is>
@@ -2318,11 +2399,15 @@
         <f>E13*G13*H13</f>
         <v/>
       </c>
-      <c r="J13" s="27">
-        <f>I13*12</f>
-        <v/>
-      </c>
-      <c r="K13" s="28" t="inlineStr">
+      <c r="J13" s="28">
+        <f>I13*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K13" s="28">
+        <f>J13*12</f>
+        <v/>
+      </c>
+      <c r="L13" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/cache/</t>
         </is>
@@ -2368,11 +2453,15 @@
         <f>E14*G14*H14</f>
         <v/>
       </c>
-      <c r="J14" s="27">
-        <f>I14*12</f>
-        <v/>
-      </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="J14" s="28">
+        <f>I14*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K14" s="28">
+        <f>J14*12</f>
+        <v/>
+      </c>
+      <c r="L14" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/storage/blobs/</t>
         </is>
@@ -2418,11 +2507,15 @@
         <f>E15*G15*H15</f>
         <v/>
       </c>
-      <c r="J15" s="27">
-        <f>I15*12</f>
-        <v/>
-      </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="J15" s="28">
+        <f>I15*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K15" s="28">
+        <f>J15*12</f>
+        <v/>
+      </c>
+      <c r="L15" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/storage/blobs/</t>
         </is>
@@ -2468,11 +2561,15 @@
         <f>E16*G16*H16</f>
         <v/>
       </c>
-      <c r="J16" s="27">
-        <f>I16*12</f>
-        <v/>
-      </c>
-      <c r="K16" s="28" t="inlineStr">
+      <c r="J16" s="28">
+        <f>I16*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K16" s="28">
+        <f>J16*12</f>
+        <v/>
+      </c>
+      <c r="L16" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/health-data-services/</t>
         </is>
@@ -2518,458 +2615,498 @@
         <f>E17*G17*H17</f>
         <v/>
       </c>
-      <c r="J17" s="27">
-        <f>I17*12</f>
-        <v/>
-      </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="J17" s="28">
+        <f>I17*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K17" s="28">
+        <f>J17*12</f>
+        <v/>
+      </c>
+      <c r="L17" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/health-data-services/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Azure Front Door</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Premium - tarifa base (incluye WAF administrado)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="19" t="n">
         <v>330</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="20">
         <f>E18*G18*H18</f>
         <v/>
       </c>
       <c r="J18" s="21">
-        <f>I18*12</f>
-        <v/>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
+        <f>I18*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>J18*12</f>
+        <v/>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/frontdoor/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Azure Front Door</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Premium - solicitudes</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>10K solicitudes</t>
         </is>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <f>Supuestos!$B$12/10000</f>
         <v/>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="19" t="n">
         <v>0.015</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="20">
         <f>E19*G19*H19</f>
         <v/>
       </c>
       <c r="J19" s="21">
-        <f>I19*12</f>
-        <v/>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
+        <f>I19*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>J19*12</f>
+        <v/>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/frontdoor/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Azure Front Door</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Premium - salida de datos (Zona 1)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="18">
         <f>Supuestos!$B$20</f>
         <v/>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="19" t="n">
         <v>0.0825</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="20">
         <f>E20*G20*H20</f>
         <v/>
       </c>
       <c r="J20" s="21">
-        <f>I20*12</f>
-        <v/>
-      </c>
-      <c r="K20" s="22" t="inlineStr">
+        <f>I20*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K20" s="21">
+        <f>J20*12</f>
+        <v/>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/frontdoor/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>API Management</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Standard v2 (1 unidad, 50M llamadas incluidas)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>unidad-hora</t>
         </is>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="19" t="n">
         <v>0.9589</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="20">
         <f>E21*G21*H21</f>
         <v/>
       </c>
       <c r="J21" s="21">
-        <f>I21*12</f>
-        <v/>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
+        <f>I21*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K21" s="21">
+        <f>J21*12</f>
+        <v/>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/api-management/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>API Management</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Standard v2 (1 unidad, región pasiva)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Central US</t>
         </is>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>unidad-hora</t>
         </is>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="19" t="n">
         <v>0.9589</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="20">
         <f>E22*G22*H22</f>
         <v/>
       </c>
       <c r="J22" s="21">
-        <f>I22*12</f>
-        <v/>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
+        <f>I22*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K22" s="21">
+        <f>J22*12</f>
+        <v/>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/api-management/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Private Endpoints</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>PostgreSQL, Redis, Service Bus, Key Vault, Blob, FHIR, OpenAI, ACR, réplicas</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>endpoint-hora</t>
         </is>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="19" t="n">
         <v>0.01</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="20">
         <f>E23*G23*H23</f>
         <v/>
       </c>
       <c r="J23" s="21">
-        <f>I23*12</f>
-        <v/>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
+        <f>I23*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K23" s="21">
+        <f>J23*12</f>
+        <v/>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/private-link/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Private Link - datos procesados</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>Entrada + salida</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="H24" s="20" t="n">
+      <c r="H24" s="19" t="n">
         <v>0.01</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="20">
         <f>E24*G24*H24</f>
         <v/>
       </c>
       <c r="J24" s="21">
-        <f>I24*12</f>
-        <v/>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
+        <f>I24*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K24" s="21">
+        <f>J24*12</f>
+        <v/>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/private-link/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Transferencia entre regiones</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Dentro de Norteamérica</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="18">
         <f>Supuestos!$B$24</f>
         <v/>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="19" t="n">
         <v>0.02</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="20">
         <f>E25*G25*H25</f>
         <v/>
       </c>
       <c r="J25" s="21">
-        <f>I25*12</f>
-        <v/>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
+        <f>I25*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K25" s="21">
+        <f>J25*12</f>
+        <v/>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/bandwidth/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Azure DNS</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>1 zona pública + 10M consultas</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="19" t="n">
         <v>4.5</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="20">
         <f>E26*G26*H26</f>
         <v/>
       </c>
       <c r="J26" s="21">
-        <f>I26*12</f>
-        <v/>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
+        <f>I26*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K26" s="21">
+        <f>J26*12</f>
+        <v/>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/dns/</t>
         </is>
@@ -3015,11 +3152,15 @@
         <f>E27*G27*H27</f>
         <v/>
       </c>
-      <c r="J27" s="27">
-        <f>I27*12</f>
-        <v/>
-      </c>
-      <c r="K27" s="28" t="inlineStr">
+      <c r="J27" s="28">
+        <f>I27*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K27" s="28">
+        <f>J27*12</f>
+        <v/>
+      </c>
+      <c r="L27" s="29" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/es-es/security/business/microsoft-entra-pricing</t>
         </is>
@@ -3064,11 +3205,15 @@
         <f>E28*G28*H28</f>
         <v/>
       </c>
-      <c r="J28" s="27">
-        <f>I28*12</f>
-        <v/>
-      </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="J28" s="28">
+        <f>I28*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K28" s="28">
+        <f>J28*12</f>
+        <v/>
+      </c>
+      <c r="L28" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/key-vault/</t>
         </is>
@@ -3115,11 +3260,15 @@
         <f>E29*G29*H29</f>
         <v/>
       </c>
-      <c r="J29" s="27">
-        <f>I29*12</f>
-        <v/>
-      </c>
-      <c r="K29" s="28" t="inlineStr">
+      <c r="J29" s="28">
+        <f>I29*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K29" s="28">
+        <f>J29*12</f>
+        <v/>
+      </c>
+      <c r="L29" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/defender-for-cloud/</t>
         </is>
@@ -3164,11 +3313,15 @@
         <f>E30*G30*H30</f>
         <v/>
       </c>
-      <c r="J30" s="27">
-        <f>I30*12</f>
-        <v/>
-      </c>
-      <c r="K30" s="28" t="inlineStr">
+      <c r="J30" s="28">
+        <f>I30*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K30" s="28">
+        <f>J30*12</f>
+        <v/>
+      </c>
+      <c r="L30" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/defender-for-cloud/</t>
         </is>
@@ -3213,308 +3366,336 @@
         <f>E31*G31*H31</f>
         <v/>
       </c>
-      <c r="J31" s="27">
-        <f>I31*12</f>
-        <v/>
-      </c>
-      <c r="K31" s="28" t="inlineStr">
+      <c r="J31" s="28">
+        <f>I31*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K31" s="28">
+        <f>J31*12</f>
+        <v/>
+      </c>
+      <c r="L31" s="29" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/frontdoor/domain</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Log Analytics + Application Insights</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Analytics Logs (5 GB gratis, 31 días de retención)</t>
         </is>
       </c>
-      <c r="D32" s="17" t="inlineStr">
+      <c r="D32" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E32" s="19" t="n">
+      <c r="E32" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="18">
         <f>MAX(0,Supuestos!$B$19-5)</f>
         <v/>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="19" t="n">
         <v>2.76</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="20">
         <f>E32*G32*H32</f>
         <v/>
       </c>
       <c r="J32" s="21">
-        <f>I32*12</f>
-        <v/>
-      </c>
-      <c r="K32" s="22" t="inlineStr">
+        <f>I32*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K32" s="21">
+        <f>J32*12</f>
+        <v/>
+      </c>
+      <c r="L32" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/monitor/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Managed Prometheus</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Ingesta de métricas</t>
         </is>
       </c>
-      <c r="D33" s="17" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E33" s="19" t="n">
+      <c r="E33" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>10M muestras</t>
         </is>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="18">
         <f>Supuestos!$B$23/10</f>
         <v/>
       </c>
-      <c r="H33" s="20" t="n">
+      <c r="H33" s="19" t="n">
         <v>0.16</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="20">
         <f>E33*G33*H33</f>
         <v/>
       </c>
       <c r="J33" s="21">
-        <f>I33*12</f>
-        <v/>
-      </c>
-      <c r="K33" s="22" t="inlineStr">
+        <f>I33*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K33" s="21">
+        <f>J33*12</f>
+        <v/>
+      </c>
+      <c r="L33" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/monitor/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Azure Managed Grafana</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Standard (instancia)</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E34" s="19" t="n">
+      <c r="E34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>hora</t>
         </is>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H34" s="20" t="n">
+      <c r="H34" s="19" t="n">
         <v>0.034246</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="20">
         <f>E34*G34*H34</f>
         <v/>
       </c>
       <c r="J34" s="21">
-        <f>I34*12</f>
-        <v/>
-      </c>
-      <c r="K34" s="22" t="inlineStr">
+        <f>I34*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K34" s="21">
+        <f>J34*12</f>
+        <v/>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/managed-grafana/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Azure Managed Grafana</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Usuarios activos</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>usuario-mes</t>
         </is>
       </c>
-      <c r="G35" s="19" t="n">
+      <c r="G35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="20" t="n">
+      <c r="H35" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="20">
         <f>E35*G35*H35</f>
         <v/>
       </c>
       <c r="J35" s="21">
-        <f>I35*12</f>
-        <v/>
-      </c>
-      <c r="K35" s="22" t="inlineStr">
+        <f>I35*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K35" s="21">
+        <f>J35*12</f>
+        <v/>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/managed-grafana/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>Alertas de logs</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Reglas cada 10 minutos</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>regla-mes</t>
         </is>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="20" t="n">
+      <c r="H36" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="20">
         <f>E36*G36*H36</f>
         <v/>
       </c>
       <c r="J36" s="21">
-        <f>I36*12</f>
-        <v/>
-      </c>
-      <c r="K36" s="22" t="inlineStr">
+        <f>I36*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K36" s="21">
+        <f>J36*12</f>
+        <v/>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/monitor/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Alertas de métricas</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>Recursos monitoreados cada 1 minuto</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E37" s="19" t="n">
+      <c r="E37" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>recurso-mes</t>
         </is>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="20" t="n">
+      <c r="H37" s="19" t="n">
         <v>0.3</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="20">
         <f>E37*G37*H37</f>
         <v/>
       </c>
       <c r="J37" s="21">
-        <f>I37*12</f>
-        <v/>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
+        <f>I37*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K37" s="21">
+        <f>J37*12</f>
+        <v/>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/monitor/</t>
         </is>
@@ -3560,11 +3741,15 @@
         <f>E38*G38*H38</f>
         <v/>
       </c>
-      <c r="J38" s="27">
-        <f>I38*12</f>
-        <v/>
-      </c>
-      <c r="K38" s="28" t="inlineStr">
+      <c r="J38" s="28">
+        <f>I38*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K38" s="28">
+        <f>J38*12</f>
+        <v/>
+      </c>
+      <c r="L38" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/service-bus/</t>
         </is>
@@ -3610,11 +3795,15 @@
         <f>E39*G39*H39</f>
         <v/>
       </c>
-      <c r="J39" s="27">
-        <f>I39*12</f>
-        <v/>
-      </c>
-      <c r="K39" s="28" t="inlineStr">
+      <c r="J39" s="28">
+        <f>I39*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K39" s="28">
+        <f>J39*12</f>
+        <v/>
+      </c>
+      <c r="L39" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/cognitive-services/openai-service/</t>
         </is>
@@ -3660,11 +3849,15 @@
         <f>E40*G40*H40</f>
         <v/>
       </c>
-      <c r="J40" s="27">
-        <f>I40*12</f>
-        <v/>
-      </c>
-      <c r="K40" s="28" t="inlineStr">
+      <c r="J40" s="28">
+        <f>I40*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K40" s="28">
+        <f>J40*12</f>
+        <v/>
+      </c>
+      <c r="L40" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/cognitive-services/openai-service/</t>
         </is>
@@ -3710,11 +3903,15 @@
         <f>E41*G41*H41</f>
         <v/>
       </c>
-      <c r="J41" s="27">
-        <f>I41*12</f>
-        <v/>
-      </c>
-      <c r="K41" s="28" t="inlineStr">
+      <c r="J41" s="28">
+        <f>I41*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K41" s="28">
+        <f>J41*12</f>
+        <v/>
+      </c>
+      <c r="L41" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/azure-maps/</t>
         </is>
@@ -3760,11 +3957,15 @@
         <f>E42*G42*H42</f>
         <v/>
       </c>
-      <c r="J42" s="27">
-        <f>I42*12</f>
-        <v/>
-      </c>
-      <c r="K42" s="28" t="inlineStr">
+      <c r="J42" s="28">
+        <f>I42*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K42" s="28">
+        <f>J42*12</f>
+        <v/>
+      </c>
+      <c r="L42" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/azure-maps/</t>
         </is>
@@ -3810,11 +4011,15 @@
         <f>E43*G43*H43</f>
         <v/>
       </c>
-      <c r="J43" s="27">
-        <f>I43*12</f>
-        <v/>
-      </c>
-      <c r="K43" s="28" t="inlineStr">
+      <c r="J43" s="28">
+        <f>I43*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K43" s="28">
+        <f>J43*12</f>
+        <v/>
+      </c>
+      <c r="L43" s="29" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/communication-services/concepts/sms-pricing</t>
         </is>
@@ -3860,11 +4065,15 @@
         <f>E44*G44*H44</f>
         <v/>
       </c>
-      <c r="J44" s="27">
-        <f>I44*12</f>
-        <v/>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
+      <c r="J44" s="28">
+        <f>I44*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K44" s="28">
+        <f>J44*12</f>
+        <v/>
+      </c>
+      <c r="L44" s="29" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/communication-services/concepts/pricing</t>
         </is>
@@ -3910,11 +4119,15 @@
         <f>E45*G45*H45</f>
         <v/>
       </c>
-      <c r="J45" s="27">
-        <f>I45*12</f>
-        <v/>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
+      <c r="J45" s="28">
+        <f>I45*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K45" s="28">
+        <f>J45*12</f>
+        <v/>
+      </c>
+      <c r="L45" s="29" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/communication-services/</t>
         </is>
@@ -3959,440 +4172,476 @@
         <f>E46*G46*H46</f>
         <v/>
       </c>
-      <c r="J46" s="27">
-        <f>I46*12</f>
-        <v/>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
+      <c r="J46" s="28">
+        <f>I46*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K46" s="28">
+        <f>J46*12</f>
+        <v/>
+      </c>
+      <c r="L46" s="29" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/communication-services/concepts/numbers/number-types</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="B47" s="31" t="inlineStr">
         <is>
           <t>AKS - nodos</t>
         </is>
       </c>
-      <c r="C47" s="30" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>Standard_D2s_v5 (2 vCPU, 8 GB), plano Free</t>
         </is>
       </c>
-      <c r="D47" s="29" t="inlineStr">
+      <c r="D47" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E47" s="31" t="n">
+      <c r="E47" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="29" t="inlineStr">
+      <c r="F47" s="30" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H47" s="32" t="n">
+      <c r="H47" s="33" t="n">
         <v>0.096</v>
       </c>
-      <c r="I47" s="33">
+      <c r="I47" s="34">
         <f>E47*G47*H47</f>
         <v/>
       </c>
-      <c r="J47" s="33">
-        <f>I47*12</f>
-        <v/>
-      </c>
-      <c r="K47" s="34" t="inlineStr">
+      <c r="J47" s="35">
+        <f>I47*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K47" s="35">
+        <f>J47*12</f>
+        <v/>
+      </c>
+      <c r="L47" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/virtual-machines/linux/</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B48" s="31" t="inlineStr">
         <is>
           <t>PostgreSQL Flexible Server</t>
         </is>
       </c>
-      <c r="C48" s="30" t="inlineStr">
+      <c r="C48" s="31" t="inlineStr">
         <is>
           <t>Burstable B2s + 64 GB</t>
         </is>
       </c>
-      <c r="D48" s="29" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E48" s="31" t="n">
+      <c r="E48" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="29" t="inlineStr">
+      <c r="F48" s="30" t="inlineStr">
         <is>
           <t>servidor-hora</t>
         </is>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H48" s="32" t="n">
+      <c r="H48" s="33" t="n">
         <v>0.068</v>
       </c>
-      <c r="I48" s="33">
+      <c r="I48" s="34">
         <f>E48*G48*H48</f>
         <v/>
       </c>
-      <c r="J48" s="33">
-        <f>I48*12</f>
-        <v/>
-      </c>
-      <c r="K48" s="34" t="inlineStr">
+      <c r="J48" s="35">
+        <f>I48*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K48" s="35">
+        <f>J48*12</f>
+        <v/>
+      </c>
+      <c r="L48" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/postgresql/flexible-server/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>PostgreSQL - almacenamiento</t>
         </is>
       </c>
-      <c r="C49" s="30" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>64 GB</t>
         </is>
       </c>
-      <c r="D49" s="29" t="inlineStr">
+      <c r="D49" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E49" s="31" t="n">
+      <c r="E49" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="29" t="inlineStr">
+      <c r="F49" s="30" t="inlineStr">
         <is>
           <t>GB-mes</t>
         </is>
       </c>
-      <c r="G49" s="31" t="n">
+      <c r="G49" s="32" t="n">
         <v>64</v>
       </c>
-      <c r="H49" s="32" t="n">
+      <c r="H49" s="33" t="n">
         <v>0.115</v>
       </c>
-      <c r="I49" s="33">
+      <c r="I49" s="34">
         <f>E49*G49*H49</f>
         <v/>
       </c>
-      <c r="J49" s="33">
-        <f>I49*12</f>
-        <v/>
-      </c>
-      <c r="K49" s="34" t="inlineStr">
+      <c r="J49" s="35">
+        <f>I49*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K49" s="35">
+        <f>J49*12</f>
+        <v/>
+      </c>
+      <c r="L49" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/postgresql/flexible-server/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>API Management</t>
         </is>
       </c>
-      <c r="C50" s="30" t="inlineStr">
+      <c r="C50" s="31" t="inlineStr">
         <is>
           <t>Basic v2</t>
         </is>
       </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E50" s="31" t="n">
+      <c r="E50" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="29" t="inlineStr">
+      <c r="F50" s="30" t="inlineStr">
         <is>
           <t>unidad-hora</t>
         </is>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H50" s="32" t="n">
+      <c r="H50" s="33" t="n">
         <v>0.20548</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <f>E50*G50*H50</f>
         <v/>
       </c>
-      <c r="J50" s="33">
-        <f>I50*12</f>
-        <v/>
-      </c>
-      <c r="K50" s="34" t="inlineStr">
+      <c r="J50" s="35">
+        <f>I50*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K50" s="35">
+        <f>J50*12</f>
+        <v/>
+      </c>
+      <c r="L50" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/api-management/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>Azure Cache for Redis</t>
         </is>
       </c>
-      <c r="C51" s="30" t="inlineStr">
+      <c r="C51" s="31" t="inlineStr">
         <is>
           <t>Basic C2</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E51" s="31" t="n">
+      <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F51" s="30" t="inlineStr">
         <is>
           <t>caché-hora</t>
         </is>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H51" s="32" t="n">
+      <c r="H51" s="33" t="n">
         <v>0.09</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <f>E51*G51*H51</f>
         <v/>
       </c>
-      <c r="J51" s="33">
-        <f>I51*12</f>
-        <v/>
-      </c>
-      <c r="K51" s="34" t="inlineStr">
+      <c r="J51" s="35">
+        <f>I51*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K51" s="35">
+        <f>J51*12</f>
+        <v/>
+      </c>
+      <c r="L51" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/cache/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>Azure Service Bus</t>
         </is>
       </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="C52" s="31" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="30" t="inlineStr">
         <is>
           <t>unidad-hora</t>
         </is>
       </c>
-      <c r="G52" s="31">
+      <c r="G52" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H52" s="32" t="n">
+      <c r="H52" s="33" t="n">
         <v>0.013441</v>
       </c>
-      <c r="I52" s="33">
+      <c r="I52" s="34">
         <f>E52*G52*H52</f>
         <v/>
       </c>
-      <c r="J52" s="33">
-        <f>I52*12</f>
-        <v/>
-      </c>
-      <c r="K52" s="34" t="inlineStr">
+      <c r="J52" s="35">
+        <f>I52*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K52" s="35">
+        <f>J52*12</f>
+        <v/>
+      </c>
+      <c r="L52" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/service-bus/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>Log Analytics</t>
         </is>
       </c>
-      <c r="C53" s="30" t="inlineStr">
+      <c r="C53" s="31" t="inlineStr">
         <is>
           <t>20 GB por mes</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="30" t="inlineStr">
         <is>
           <t>East US 2</t>
         </is>
       </c>
-      <c r="E53" s="31" t="n">
+      <c r="E53" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="29" t="inlineStr">
+      <c r="F53" s="30" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G53" s="31" t="n">
+      <c r="G53" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="H53" s="32" t="n">
+      <c r="H53" s="33" t="n">
         <v>2.76</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <f>E53*G53*H53</f>
         <v/>
       </c>
-      <c r="J53" s="33">
-        <f>I53*12</f>
-        <v/>
-      </c>
-      <c r="K53" s="34" t="inlineStr">
+      <c r="J53" s="35">
+        <f>I53*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K53" s="35">
+        <f>J53*12</f>
+        <v/>
+      </c>
+      <c r="L53" s="36" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/monitor/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35" t="inlineStr">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>TOTAL MENSUAL / ANUAL</t>
         </is>
       </c>
-      <c r="B54" s="35" t="n"/>
-      <c r="C54" s="35" t="n"/>
-      <c r="D54" s="35" t="n"/>
-      <c r="E54" s="35" t="n"/>
-      <c r="F54" s="35" t="n"/>
-      <c r="G54" s="35" t="n"/>
-      <c r="H54" s="35" t="n"/>
-      <c r="I54" s="36">
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="37" t="n"/>
+      <c r="D54" s="37" t="n"/>
+      <c r="E54" s="37" t="n"/>
+      <c r="F54" s="37" t="n"/>
+      <c r="G54" s="37" t="n"/>
+      <c r="H54" s="37" t="n"/>
+      <c r="I54" s="38">
         <f>SUM(I4:I53)</f>
         <v/>
       </c>
-      <c r="J54" s="36">
+      <c r="J54" s="39">
         <f>SUM(J4:J53)</f>
         <v/>
       </c>
-      <c r="K54" s="35" t="n"/>
+      <c r="K54" s="39">
+        <f>SUM(K4:K53)</f>
+        <v/>
+      </c>
+      <c r="L54" s="37" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K53"/>
+  <autoFilter ref="A3:L53"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4404,7 +4653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4416,8 +4665,9 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4482,261 +4732,286 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Costo anual (USD)</t>
+          <t>Costo mensual (COP)</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
+          <t>Costo anual (COP)</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>Referencia</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>Amazon EKS</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Plano de control estándar</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>us-east-2 + us-west-2</t>
         </is>
       </c>
-      <c r="E4" s="19" t="n">
+      <c r="E4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>clúster-hora</t>
         </is>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H4" s="20" t="n">
+      <c r="H4" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="20">
         <f>E4*G4*H4</f>
         <v/>
       </c>
       <c r="J4" s="21">
-        <f>I4*12</f>
-        <v/>
-      </c>
-      <c r="K4" s="22" t="inlineStr">
+        <f>I4*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>J4*12</f>
+        <v/>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/eks/pricing/</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>EKS - nodos región primaria</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>m6i.xlarge Linux (4 vCPU, 16 GB)</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="18">
         <f>Supuestos!$B$25</f>
         <v/>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="19" t="n">
         <v>0.192</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="20">
         <f>E5*G5*H5</f>
         <v/>
       </c>
       <c r="J5" s="21">
-        <f>I5*12</f>
-        <v/>
-      </c>
-      <c r="K5" s="22" t="inlineStr">
+        <f>I5*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>J5*12</f>
+        <v/>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ec2/pricing/on-demand/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>EKS - nodos región secundaria</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>m6i.xlarge Linux (4 vCPU, 16 GB)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>us-west-2</t>
         </is>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <f>Supuestos!$B$26</f>
         <v/>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="19" t="n">
         <v>0.192</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <f>E6*G6*H6</f>
         <v/>
       </c>
       <c r="J6" s="21">
-        <f>I6*12</f>
-        <v/>
-      </c>
-      <c r="K6" s="22" t="inlineStr">
+        <f>I6*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>J6*12</f>
+        <v/>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ec2/pricing/on-demand/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>EBS de los nodos</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>gp3 128 GB</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <f>(Supuestos!$B$25+Supuestos!$B$26)*128</f>
         <v/>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>GB-mes</t>
         </is>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="20">
         <f>E7*G7*H7</f>
         <v/>
       </c>
       <c r="J7" s="21">
-        <f>I7*12</f>
-        <v/>
-      </c>
-      <c r="K7" s="22" t="inlineStr">
+        <f>I7*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>J7*12</f>
+        <v/>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ebs/pricing/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Computación</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Amazon ECR</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Almacenamiento de imágenes + replicación</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>GB-mes</t>
         </is>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="20">
         <f>E8*G8*H8</f>
         <v/>
       </c>
       <c r="J8" s="21">
-        <f>I8*12</f>
-        <v/>
-      </c>
-      <c r="K8" s="22" t="inlineStr">
+        <f>I8*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>J8*12</f>
+        <v/>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ecr/pricing/</t>
         </is>
@@ -4782,11 +5057,15 @@
         <f>E9*G9*H9</f>
         <v/>
       </c>
-      <c r="J9" s="27">
-        <f>I9*12</f>
-        <v/>
-      </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="J9" s="28">
+        <f>I9*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="28">
+        <f>J9*12</f>
+        <v/>
+      </c>
+      <c r="L9" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
@@ -4832,11 +5111,15 @@
         <f>E10*G10*H10</f>
         <v/>
       </c>
-      <c r="J10" s="27">
-        <f>I10*12</f>
-        <v/>
-      </c>
-      <c r="K10" s="28" t="inlineStr">
+      <c r="J10" s="28">
+        <f>I10*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K10" s="28">
+        <f>J10*12</f>
+        <v/>
+      </c>
+      <c r="L10" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
@@ -4882,11 +5165,15 @@
         <f>E11*G11*H11</f>
         <v/>
       </c>
-      <c r="J11" s="27">
-        <f>I11*12</f>
-        <v/>
-      </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="J11" s="28">
+        <f>I11*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K11" s="28">
+        <f>J11*12</f>
+        <v/>
+      </c>
+      <c r="L11" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
@@ -4932,11 +5219,15 @@
         <f>E12*G12*H12</f>
         <v/>
       </c>
-      <c r="J12" s="27">
-        <f>I12*12</f>
-        <v/>
-      </c>
-      <c r="K12" s="28" t="inlineStr">
+      <c r="J12" s="28">
+        <f>I12*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K12" s="28">
+        <f>J12*12</f>
+        <v/>
+      </c>
+      <c r="L12" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
@@ -4982,11 +5273,15 @@
         <f>E13*G13*H13</f>
         <v/>
       </c>
-      <c r="J13" s="27">
-        <f>I13*12</f>
-        <v/>
-      </c>
-      <c r="K13" s="28" t="inlineStr">
+      <c r="J13" s="28">
+        <f>I13*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K13" s="28">
+        <f>J13*12</f>
+        <v/>
+      </c>
+      <c r="L13" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/elasticache/pricing/</t>
         </is>
@@ -5032,11 +5327,15 @@
         <f>E14*G14*H14</f>
         <v/>
       </c>
-      <c r="J14" s="27">
-        <f>I14*12</f>
-        <v/>
-      </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="J14" s="28">
+        <f>I14*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K14" s="28">
+        <f>J14*12</f>
+        <v/>
+      </c>
+      <c r="L14" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/s3/pricing/</t>
         </is>
@@ -5082,11 +5381,15 @@
         <f>E15*G15*H15</f>
         <v/>
       </c>
-      <c r="J15" s="27">
-        <f>I15*12</f>
-        <v/>
-      </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="J15" s="28">
+        <f>I15*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K15" s="28">
+        <f>J15*12</f>
+        <v/>
+      </c>
+      <c r="L15" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/s3/pricing/</t>
         </is>
@@ -5132,11 +5435,15 @@
         <f>E16*G16*H16</f>
         <v/>
       </c>
-      <c r="J16" s="27">
-        <f>I16*12</f>
-        <v/>
-      </c>
-      <c r="K16" s="28" t="inlineStr">
+      <c r="J16" s="28">
+        <f>I16*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K16" s="28">
+        <f>J16*12</f>
+        <v/>
+      </c>
+      <c r="L16" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/healthlake/pricing/</t>
         </is>
@@ -5182,459 +5489,499 @@
         <f>E17*G17*H17</f>
         <v/>
       </c>
-      <c r="J17" s="27">
-        <f>I17*12</f>
-        <v/>
-      </c>
-      <c r="K17" s="28" t="inlineStr">
+      <c r="J17" s="28">
+        <f>I17*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K17" s="28">
+        <f>J17*12</f>
+        <v/>
+      </c>
+      <c r="L17" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/healthlake/pricing/</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Amazon CloudFront</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Salida de datos (primeros 10 TB)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="18">
         <f>Supuestos!$B$20</f>
         <v/>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="19" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="20">
         <f>E18*G18*H18</f>
         <v/>
       </c>
       <c r="J18" s="21">
-        <f>I18*12</f>
-        <v/>
-      </c>
-      <c r="K18" s="22" t="inlineStr">
+        <f>I18*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>J18*12</f>
+        <v/>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudfront/pricing/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Amazon CloudFront</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Solicitudes HTTPS</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>10K solicitudes</t>
         </is>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <f>Supuestos!$B$12/10000</f>
         <v/>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="19" t="n">
         <v>0.01</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="20">
         <f>E19*G19*H19</f>
         <v/>
       </c>
       <c r="J19" s="21">
-        <f>I19*12</f>
-        <v/>
-      </c>
-      <c r="K19" s="22" t="inlineStr">
+        <f>I19*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>J19*12</f>
+        <v/>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudfront/pricing/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Amazon API Gateway</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>HTTP API</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>1M solicitudes</t>
         </is>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="18">
         <f>Supuestos!$B$12/1000000</f>
         <v/>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="20">
         <f>E20*G20*H20</f>
         <v/>
       </c>
       <c r="J20" s="21">
-        <f>I20*12</f>
-        <v/>
-      </c>
-      <c r="K20" s="22" t="inlineStr">
+        <f>I20*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K20" s="21">
+        <f>J20*12</f>
+        <v/>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/api-gateway/pricing/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Application Load Balancer</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>1 por región (hora + LCU estimado)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>ALB-hora</t>
         </is>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="19" t="n">
         <v>0.0385</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="20">
         <f>E21*G21*H21</f>
         <v/>
       </c>
       <c r="J21" s="21">
-        <f>I21*12</f>
-        <v/>
-      </c>
-      <c r="K21" s="22" t="inlineStr">
+        <f>I21*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K21" s="21">
+        <f>J21*12</f>
+        <v/>
+      </c>
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/elasticloadbalancing/pricing/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>NAT Gateway</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>1 por región</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>gateway-hora</t>
         </is>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="20">
         <f>E22*G22*H22</f>
         <v/>
       </c>
       <c r="J22" s="21">
-        <f>I22*12</f>
-        <v/>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
+        <f>I22*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K22" s="21">
+        <f>J22*12</f>
+        <v/>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/vpc/pricing/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>NAT Gateway - datos procesados</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Tráfico saliente de los nodos</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="18" t="n">
         <v>200</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="19" t="n">
         <v>0.045</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="20">
         <f>E23*G23*H23</f>
         <v/>
       </c>
       <c r="J23" s="21">
-        <f>I23*12</f>
-        <v/>
-      </c>
-      <c r="K23" s="22" t="inlineStr">
+        <f>I23*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K23" s="21">
+        <f>J23*12</f>
+        <v/>
+      </c>
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/vpc/pricing/</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>VPC Interface Endpoints (PrivateLink)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>8 endpoints x 2 zonas</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>endpoint-hora</t>
         </is>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="18">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H24" s="20" t="n">
+      <c r="H24" s="19" t="n">
         <v>0.01</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="20">
         <f>E24*G24*H24</f>
         <v/>
       </c>
       <c r="J24" s="21">
-        <f>I24*12</f>
-        <v/>
-      </c>
-      <c r="K24" s="22" t="inlineStr">
+        <f>I24*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K24" s="21">
+        <f>J24*12</f>
+        <v/>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/privatelink/pricing/</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Transferencia entre regiones</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>us-east-2 a us-west-2</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Ambas</t>
         </is>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="18">
         <f>Supuestos!$B$24</f>
         <v/>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="19" t="n">
         <v>0.02</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="20">
         <f>E25*G25*H25</f>
         <v/>
       </c>
       <c r="J25" s="21">
-        <f>I25*12</f>
-        <v/>
-      </c>
-      <c r="K25" s="22" t="inlineStr">
+        <f>I25*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K25" s="21">
+        <f>J25*12</f>
+        <v/>
+      </c>
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ec2/pricing/on-demand/#Data_Transfer</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Redes</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Amazon Route 53</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>1 zona, 2 health checks, 10M consultas</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="20">
         <f>E26*G26*H26</f>
         <v/>
       </c>
       <c r="J26" s="21">
-        <f>I26*12</f>
-        <v/>
-      </c>
-      <c r="K26" s="22" t="inlineStr">
+        <f>I26*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K26" s="21">
+        <f>J26*12</f>
+        <v/>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/route53/pricing/</t>
         </is>
@@ -5680,11 +6027,15 @@
         <f>E27*G27*H27</f>
         <v/>
       </c>
-      <c r="J27" s="27">
-        <f>I27*12</f>
-        <v/>
-      </c>
-      <c r="K27" s="28" t="inlineStr">
+      <c r="J27" s="28">
+        <f>I27*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K27" s="28">
+        <f>J27*12</f>
+        <v/>
+      </c>
+      <c r="L27" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cognito/pricing/</t>
         </is>
@@ -5729,11 +6080,15 @@
         <f>E28*G28*H28</f>
         <v/>
       </c>
-      <c r="J28" s="27">
-        <f>I28*12</f>
-        <v/>
-      </c>
-      <c r="K28" s="28" t="inlineStr">
+      <c r="J28" s="28">
+        <f>I28*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K28" s="28">
+        <f>J28*12</f>
+        <v/>
+      </c>
+      <c r="L28" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/waf/pricing/</t>
         </is>
@@ -5779,11 +6134,15 @@
         <f>E29*G29*H29</f>
         <v/>
       </c>
-      <c r="J29" s="27">
-        <f>I29*12</f>
-        <v/>
-      </c>
-      <c r="K29" s="28" t="inlineStr">
+      <c r="J29" s="28">
+        <f>I29*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K29" s="28">
+        <f>J29*12</f>
+        <v/>
+      </c>
+      <c r="L29" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/waf/pricing/</t>
         </is>
@@ -5828,11 +6187,15 @@
         <f>E30*G30*H30</f>
         <v/>
       </c>
-      <c r="J30" s="27">
-        <f>I30*12</f>
-        <v/>
-      </c>
-      <c r="K30" s="28" t="inlineStr">
+      <c r="J30" s="28">
+        <f>I30*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K30" s="28">
+        <f>J30*12</f>
+        <v/>
+      </c>
+      <c r="L30" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/secrets-manager/pricing/</t>
         </is>
@@ -5878,11 +6241,15 @@
         <f>E31*G31*H31</f>
         <v/>
       </c>
-      <c r="J31" s="27">
-        <f>I31*12</f>
-        <v/>
-      </c>
-      <c r="K31" s="28" t="inlineStr">
+      <c r="J31" s="28">
+        <f>I31*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K31" s="28">
+        <f>J31*12</f>
+        <v/>
+      </c>
+      <c r="L31" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/guardduty/pricing/</t>
         </is>
@@ -5927,11 +6294,15 @@
         <f>E32*G32*H32</f>
         <v/>
       </c>
-      <c r="J32" s="27">
-        <f>I32*12</f>
-        <v/>
-      </c>
-      <c r="K32" s="28" t="inlineStr">
+      <c r="J32" s="28">
+        <f>I32*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K32" s="28">
+        <f>J32*12</f>
+        <v/>
+      </c>
+      <c r="L32" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/security-hub/pricing/</t>
         </is>
@@ -5976,308 +6347,336 @@
         <f>E33*G33*H33</f>
         <v/>
       </c>
-      <c r="J33" s="27">
-        <f>I33*12</f>
-        <v/>
-      </c>
-      <c r="K33" s="28" t="inlineStr">
+      <c r="J33" s="28">
+        <f>I33*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K33" s="28">
+        <f>J33*12</f>
+        <v/>
+      </c>
+      <c r="L33" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/certificate-manager/pricing/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>CloudWatch Logs</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Ingesta</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E34" s="19" t="n">
+      <c r="E34" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="18">
         <f>Supuestos!$B$19</f>
         <v/>
       </c>
-      <c r="H34" s="20" t="n">
+      <c r="H34" s="19" t="n">
         <v>0.5</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="20">
         <f>E34*G34*H34</f>
         <v/>
       </c>
       <c r="J34" s="21">
-        <f>I34*12</f>
-        <v/>
-      </c>
-      <c r="K34" s="22" t="inlineStr">
+        <f>I34*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K34" s="21">
+        <f>J34*12</f>
+        <v/>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudwatch/pricing/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>CloudWatch Logs</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Almacenamiento</t>
         </is>
       </c>
-      <c r="D35" s="17" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>GB-mes</t>
         </is>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="18">
         <f>Supuestos!$B$19</f>
         <v/>
       </c>
-      <c r="H35" s="20" t="n">
+      <c r="H35" s="19" t="n">
         <v>0.03</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="20">
         <f>E35*G35*H35</f>
         <v/>
       </c>
       <c r="J35" s="21">
-        <f>I35*12</f>
-        <v/>
-      </c>
-      <c r="K35" s="22" t="inlineStr">
+        <f>I35*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K35" s="21">
+        <f>J35*12</f>
+        <v/>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudwatch/pricing/</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>Amazon Managed Service for Prometheus</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Ingesta de métricas</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>10M muestras</t>
         </is>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="18">
         <f>Supuestos!$B$23/10</f>
         <v/>
       </c>
-      <c r="H36" s="20" t="n">
+      <c r="H36" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="20">
         <f>E36*G36*H36</f>
         <v/>
       </c>
       <c r="J36" s="21">
-        <f>I36*12</f>
-        <v/>
-      </c>
-      <c r="K36" s="22" t="inlineStr">
+        <f>I36*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K36" s="21">
+        <f>J36*12</f>
+        <v/>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/prometheus/pricing/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>Amazon Managed Grafana</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>2 editores + 5 visualizadores</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E37" s="19" t="n">
+      <c r="E37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="20" t="n">
+      <c r="H37" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="20">
         <f>E37*G37*H37</f>
         <v/>
       </c>
       <c r="J37" s="21">
-        <f>I37*12</f>
-        <v/>
-      </c>
-      <c r="K37" s="22" t="inlineStr">
+        <f>I37*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K37" s="21">
+        <f>J37*12</f>
+        <v/>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/grafana/pricing/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>CloudWatch Alarms</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="17" t="inlineStr">
         <is>
           <t>Alarmas estándar</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>alarma-mes</t>
         </is>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="G38" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="20" t="n">
+      <c r="H38" s="19" t="n">
         <v>0.1</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="20">
         <f>E38*G38*H38</f>
         <v/>
       </c>
       <c r="J38" s="21">
-        <f>I38*12</f>
-        <v/>
-      </c>
-      <c r="K38" s="22" t="inlineStr">
+        <f>I38*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K38" s="21">
+        <f>J38*12</f>
+        <v/>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudwatch/pricing/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Monitoreo y Logs</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>AWS X-Ray</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>Trazas (100K gratis)</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E39" s="19" t="n">
+      <c r="E39" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>1M trazas</t>
         </is>
       </c>
-      <c r="G39" s="19" t="n">
+      <c r="G39" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="20">
         <f>E39*G39*H39</f>
         <v/>
       </c>
       <c r="J39" s="21">
-        <f>I39*12</f>
-        <v/>
-      </c>
-      <c r="K39" s="22" t="inlineStr">
+        <f>I39*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K39" s="21">
+        <f>J39*12</f>
+        <v/>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/xray/pricing/</t>
         </is>
@@ -6322,11 +6721,15 @@
         <f>E40*G40*H40</f>
         <v/>
       </c>
-      <c r="J40" s="27">
-        <f>I40*12</f>
-        <v/>
-      </c>
-      <c r="K40" s="28" t="inlineStr">
+      <c r="J40" s="28">
+        <f>I40*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K40" s="28">
+        <f>J40*12</f>
+        <v/>
+      </c>
+      <c r="L40" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/sqs/pricing/</t>
         </is>
@@ -6372,11 +6775,15 @@
         <f>E41*G41*H41</f>
         <v/>
       </c>
-      <c r="J41" s="27">
-        <f>I41*12</f>
-        <v/>
-      </c>
-      <c r="K41" s="28" t="inlineStr">
+      <c r="J41" s="28">
+        <f>I41*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K41" s="28">
+        <f>J41*12</f>
+        <v/>
+      </c>
+      <c r="L41" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/bedrock/pricing/</t>
         </is>
@@ -6422,11 +6829,15 @@
         <f>E42*G42*H42</f>
         <v/>
       </c>
-      <c r="J42" s="27">
-        <f>I42*12</f>
-        <v/>
-      </c>
-      <c r="K42" s="28" t="inlineStr">
+      <c r="J42" s="28">
+        <f>I42*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K42" s="28">
+        <f>J42*12</f>
+        <v/>
+      </c>
+      <c r="L42" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/bedrock/pricing/</t>
         </is>
@@ -6472,11 +6883,15 @@
         <f>E43*G43*H43</f>
         <v/>
       </c>
-      <c r="J43" s="27">
-        <f>I43*12</f>
-        <v/>
-      </c>
-      <c r="K43" s="28" t="inlineStr">
+      <c r="J43" s="28">
+        <f>I43*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K43" s="28">
+        <f>J43*12</f>
+        <v/>
+      </c>
+      <c r="L43" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/location/pricing/</t>
         </is>
@@ -6522,11 +6937,15 @@
         <f>E44*G44*H44</f>
         <v/>
       </c>
-      <c r="J44" s="27">
-        <f>I44*12</f>
-        <v/>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
+      <c r="J44" s="28">
+        <f>I44*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K44" s="28">
+        <f>J44*12</f>
+        <v/>
+      </c>
+      <c r="L44" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/location/pricing/</t>
         </is>
@@ -6572,11 +6991,15 @@
         <f>E45*G45*H45</f>
         <v/>
       </c>
-      <c r="J45" s="27">
-        <f>I45*12</f>
-        <v/>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
+      <c r="J45" s="28">
+        <f>I45*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K45" s="28">
+        <f>J45*12</f>
+        <v/>
+      </c>
+      <c r="L45" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/end-user-messaging/pricing/</t>
         </is>
@@ -6622,11 +7045,15 @@
         <f>E46*G46*H46</f>
         <v/>
       </c>
-      <c r="J46" s="27">
-        <f>I46*12</f>
-        <v/>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
+      <c r="J46" s="28">
+        <f>I46*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K46" s="28">
+        <f>J46*12</f>
+        <v/>
+      </c>
+      <c r="L46" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/connect/pricing/</t>
         </is>
@@ -6672,11 +7099,15 @@
         <f>E47*G47*H47</f>
         <v/>
       </c>
-      <c r="J47" s="27">
-        <f>I47*12</f>
-        <v/>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
+      <c r="J47" s="28">
+        <f>I47*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K47" s="28">
+        <f>J47*12</f>
+        <v/>
+      </c>
+      <c r="L47" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ses/pricing/</t>
         </is>
@@ -6722,442 +7153,478 @@
         <f>E48*G48*H48</f>
         <v/>
       </c>
-      <c r="J48" s="27">
-        <f>I48*12</f>
-        <v/>
-      </c>
-      <c r="K48" s="28" t="inlineStr">
+      <c r="J48" s="28">
+        <f>I48*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K48" s="28">
+        <f>J48*12</f>
+        <v/>
+      </c>
+      <c r="L48" s="29" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/connect/pricing/</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>EKS</t>
         </is>
       </c>
-      <c r="C49" s="30" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>Plano de control</t>
         </is>
       </c>
-      <c r="D49" s="29" t="inlineStr">
+      <c r="D49" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E49" s="31" t="n">
+      <c r="E49" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="29" t="inlineStr">
+      <c r="F49" s="30" t="inlineStr">
         <is>
           <t>clúster-hora</t>
         </is>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H49" s="32" t="n">
+      <c r="H49" s="33" t="n">
         <v>0.1</v>
       </c>
-      <c r="I49" s="33">
+      <c r="I49" s="34">
         <f>E49*G49*H49</f>
         <v/>
       </c>
-      <c r="J49" s="33">
-        <f>I49*12</f>
-        <v/>
-      </c>
-      <c r="K49" s="34" t="inlineStr">
+      <c r="J49" s="35">
+        <f>I49*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K49" s="35">
+        <f>J49*12</f>
+        <v/>
+      </c>
+      <c r="L49" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/eks/pricing/</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>EKS - nodos</t>
         </is>
       </c>
-      <c r="C50" s="30" t="inlineStr">
+      <c r="C50" s="31" t="inlineStr">
         <is>
           <t>m6i.large (2 vCPU, 8 GB)</t>
         </is>
       </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E50" s="31" t="n">
+      <c r="E50" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="29" t="inlineStr">
+      <c r="F50" s="30" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H50" s="32" t="n">
+      <c r="H50" s="33" t="n">
         <v>0.096</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <f>E50*G50*H50</f>
         <v/>
       </c>
-      <c r="J50" s="33">
-        <f>I50*12</f>
-        <v/>
-      </c>
-      <c r="K50" s="34" t="inlineStr">
+      <c r="J50" s="35">
+        <f>I50*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K50" s="35">
+        <f>J50*12</f>
+        <v/>
+      </c>
+      <c r="L50" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ec2/pricing/on-demand/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>RDS for PostgreSQL</t>
         </is>
       </c>
-      <c r="C51" s="30" t="inlineStr">
+      <c r="C51" s="31" t="inlineStr">
         <is>
           <t>db.t4g.small Single-AZ + 64 GB</t>
         </is>
       </c>
-      <c r="D51" s="29" t="inlineStr">
+      <c r="D51" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E51" s="31" t="n">
+      <c r="E51" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F51" s="29" t="inlineStr">
+      <c r="F51" s="30" t="inlineStr">
         <is>
           <t>instancia-hora</t>
         </is>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H51" s="32" t="n">
+      <c r="H51" s="33" t="n">
         <v>0.032</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <f>E51*G51*H51</f>
         <v/>
       </c>
-      <c r="J51" s="33">
-        <f>I51*12</f>
-        <v/>
-      </c>
-      <c r="K51" s="34" t="inlineStr">
+      <c r="J51" s="35">
+        <f>I51*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K51" s="35">
+        <f>J51*12</f>
+        <v/>
+      </c>
+      <c r="L51" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>RDS - almacenamiento</t>
         </is>
       </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="C52" s="31" t="inlineStr">
         <is>
           <t>64 GB gp3</t>
         </is>
       </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E52" s="31" t="n">
+      <c r="E52" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="29" t="inlineStr">
+      <c r="F52" s="30" t="inlineStr">
         <is>
           <t>GB-mes</t>
         </is>
       </c>
-      <c r="G52" s="31" t="n">
+      <c r="G52" s="32" t="n">
         <v>64</v>
       </c>
-      <c r="H52" s="32" t="n">
+      <c r="H52" s="33" t="n">
         <v>0.115</v>
       </c>
-      <c r="I52" s="33">
+      <c r="I52" s="34">
         <f>E52*G52*H52</f>
         <v/>
       </c>
-      <c r="J52" s="33">
-        <f>I52*12</f>
-        <v/>
-      </c>
-      <c r="K52" s="34" t="inlineStr">
+      <c r="J52" s="35">
+        <f>I52*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K52" s="35">
+        <f>J52*12</f>
+        <v/>
+      </c>
+      <c r="L52" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B53" s="30" t="inlineStr">
+      <c r="B53" s="31" t="inlineStr">
         <is>
           <t>ElastiCache</t>
         </is>
       </c>
-      <c r="C53" s="30" t="inlineStr">
+      <c r="C53" s="31" t="inlineStr">
         <is>
           <t>cache.t4g.small</t>
         </is>
       </c>
-      <c r="D53" s="29" t="inlineStr">
+      <c r="D53" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E53" s="31" t="n">
+      <c r="E53" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="29" t="inlineStr">
+      <c r="F53" s="30" t="inlineStr">
         <is>
           <t>nodo-hora</t>
         </is>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H53" s="32" t="n">
+      <c r="H53" s="33" t="n">
         <v>0.032</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <f>E53*G53*H53</f>
         <v/>
       </c>
-      <c r="J53" s="33">
-        <f>I53*12</f>
-        <v/>
-      </c>
-      <c r="K53" s="34" t="inlineStr">
+      <c r="J53" s="35">
+        <f>I53*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K53" s="35">
+        <f>J53*12</f>
+        <v/>
+      </c>
+      <c r="L53" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/elasticache/pricing/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B54" s="30" t="inlineStr">
+      <c r="B54" s="31" t="inlineStr">
         <is>
           <t>NAT Gateway</t>
         </is>
       </c>
-      <c r="C54" s="30" t="inlineStr">
+      <c r="C54" s="31" t="inlineStr">
         <is>
           <t>1 gateway</t>
         </is>
       </c>
-      <c r="D54" s="29" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E54" s="31" t="n">
+      <c r="E54" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="29" t="inlineStr">
+      <c r="F54" s="30" t="inlineStr">
         <is>
           <t>gateway-hora</t>
         </is>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <f>Supuestos!$B$4</f>
         <v/>
       </c>
-      <c r="H54" s="32" t="n">
+      <c r="H54" s="33" t="n">
         <v>0.045</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="34">
         <f>E54*G54*H54</f>
         <v/>
       </c>
-      <c r="J54" s="33">
-        <f>I54*12</f>
-        <v/>
-      </c>
-      <c r="K54" s="34" t="inlineStr">
+      <c r="J54" s="35">
+        <f>I54*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K54" s="35">
+        <f>J54*12</f>
+        <v/>
+      </c>
+      <c r="L54" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/vpc/pricing/</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>Ambiente Dev/Test</t>
         </is>
       </c>
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B55" s="31" t="inlineStr">
         <is>
           <t>CloudWatch Logs</t>
         </is>
       </c>
-      <c r="C55" s="30" t="inlineStr">
+      <c r="C55" s="31" t="inlineStr">
         <is>
           <t>20 GB por mes</t>
         </is>
       </c>
-      <c r="D55" s="29" t="inlineStr">
+      <c r="D55" s="30" t="inlineStr">
         <is>
           <t>us-east-2</t>
         </is>
       </c>
-      <c r="E55" s="31" t="n">
+      <c r="E55" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F55" s="29" t="inlineStr">
+      <c r="F55" s="30" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G55" s="31" t="n">
+      <c r="G55" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="H55" s="32" t="n">
+      <c r="H55" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="I55" s="33">
+      <c r="I55" s="34">
         <f>E55*G55*H55</f>
         <v/>
       </c>
-      <c r="J55" s="33">
-        <f>I55*12</f>
-        <v/>
-      </c>
-      <c r="K55" s="34" t="inlineStr">
+      <c r="J55" s="35">
+        <f>I55*Supuestos!$B$28</f>
+        <v/>
+      </c>
+      <c r="K55" s="35">
+        <f>J55*12</f>
+        <v/>
+      </c>
+      <c r="L55" s="36" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudwatch/pricing/</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>TOTAL MENSUAL / ANUAL</t>
         </is>
       </c>
-      <c r="B56" s="35" t="n"/>
-      <c r="C56" s="35" t="n"/>
-      <c r="D56" s="35" t="n"/>
-      <c r="E56" s="35" t="n"/>
-      <c r="F56" s="35" t="n"/>
-      <c r="G56" s="35" t="n"/>
-      <c r="H56" s="35" t="n"/>
-      <c r="I56" s="36">
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="37" t="n"/>
+      <c r="D56" s="37" t="n"/>
+      <c r="E56" s="37" t="n"/>
+      <c r="F56" s="37" t="n"/>
+      <c r="G56" s="37" t="n"/>
+      <c r="H56" s="37" t="n"/>
+      <c r="I56" s="38">
         <f>SUM(I4:I55)</f>
         <v/>
       </c>
-      <c r="J56" s="36">
+      <c r="J56" s="39">
         <f>SUM(J4:J55)</f>
         <v/>
       </c>
-      <c r="K56" s="35" t="n"/>
+      <c r="K56" s="39">
+        <f>SUM(K4:K55)</f>
+        <v/>
+      </c>
+      <c r="L56" s="37" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K55"/>
+  <autoFilter ref="A3:L55"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7189,7 +7656,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Escenarios sobre el costo de pago por uso. Los porcentajes de reserva provienen de los precios oficiales de Azure Reservations (East US 2).</t>
+          <t>Escenarios en pesos colombianos (COP) sobre el costo de pago por uso. Los descuentos de reserva provienen de los precios oficiales de Azure Reservations (East US 2).</t>
         </is>
       </c>
     </row>
@@ -7201,17 +7668,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Pago por uso (mensual)</t>
+          <t>Pago por uso (COP/mes)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Optimizado 1 año (mensual)</t>
+          <t>Reservas 1 año (COP/mes)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Optimizado 3 años (mensual)</t>
+          <t>Reservas 3 años (COP/mes)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -7227,7 +7694,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>(SUMIF(Azure!$B$4:$B$53,"AKS - nodos región primaria",Azure!$I$4:$I$53)+SUMIF(Azure!$B$4:$B$53,"AKS - nodos región secundaria",Azure!$I$4:$I$53))</f>
+        <f>(SUMIF(Azure!$B$4:$B$53,"AKS - nodos región primaria",Azure!$J$4:$J$53)+SUMIF(Azure!$B$4:$B$53,"AKS - nodos región secundaria",Azure!$J$4:$J$53))</f>
         <v/>
       </c>
       <c r="C5" s="5">
@@ -7238,9 +7705,9 @@
         <f>B5*1993/(0.192*8760*3)</f>
         <v/>
       </c>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>Instancias reservadas: 1 año = $1.038/año, 3 años = $1.993 por nodo (vs $1.682/año pago por uso)</t>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>Instancias reservadas por nodo: 1 año = USD 1.038, 3 años = USD 1.993 (vs USD 1.682 por año en pago por uso)</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7718,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>(SUMIF(Azure!$B$4:$B$53,"PostgreSQL Flexible Server",Azure!$I$4:$I$53)-SUMIFS(Azure!$I$4:$I$53,Azure!$A$4:$A$53,"Ambiente Dev/Test",Azure!$B$4:$B$53,"PostgreSQL Flexible Server")+SUMIF(Azure!$B$4:$B$53,"PostgreSQL - réplica geográfica",Azure!$I$4:$I$53))</f>
+        <f>(SUMIF(Azure!$B$4:$B$53,"PostgreSQL Flexible Server",Azure!$J$4:$J$53)-SUMIFS(Azure!$J$4:$J$53,Azure!$A$4:$A$53,"Ambiente Dev/Test",Azure!$B$4:$B$53,"PostgreSQL Flexible Server")+SUMIF(Azure!$B$4:$B$53,"PostgreSQL - réplica geográfica",Azure!$J$4:$J$53))</f>
         <v/>
       </c>
       <c r="C6" s="5">
@@ -7262,9 +7729,9 @@
         <f>B6*936/(0.089*8760*3)</f>
         <v/>
       </c>
-      <c r="E6" s="37" t="inlineStr">
-        <is>
-          <t>Capacidad reservada por vCore: 1 año = $468, 3 años = $936 (vs $780/año pago por uso)</t>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>Capacidad reservada por vCore: 1 año = USD 468, 3 años = USD 936 (vs USD 780 por año en pago por uso)</t>
         </is>
       </c>
     </row>
@@ -7275,7 +7742,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>SUMIFS(Azure!$I$4:$I$53,Azure!$A$4:$A$53,"Almacenamiento y Bases de Datos",Azure!$B$4:$B$53,"Azure Cache for Redis")</f>
+        <f>SUMIFS(Azure!$J$4:$J$53,Azure!$A$4:$A$53,"Almacenamiento y Bases de Datos",Azure!$B$4:$B$53,"Azure Cache for Redis")</f>
         <v/>
       </c>
       <c r="C7" s="5">
@@ -7286,7 +7753,7 @@
         <f>B7*(1-0.55)</f>
         <v/>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="40" t="inlineStr">
         <is>
           <t>Reserva de caché Premium (~35% a 1 año, ~55% a 3 años)</t>
         </is>
@@ -7299,7 +7766,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>SUMIFS(Azure!$I$4:$I$53,Azure!$A$4:$A$53,"Monitoreo y Logs",Azure!$B$4:$B$53,"Log Analytics + Application Insights")</f>
+        <f>SUMIFS(Azure!$J$4:$J$53,Azure!$A$4:$A$53,"Monitoreo y Logs",Azure!$B$4:$B$53,"Log Analytics + Application Insights")</f>
         <v/>
       </c>
       <c r="C8" s="5">
@@ -7310,7 +7777,7 @@
         <f>B8*(1-0.40)</f>
         <v/>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="40" t="inlineStr">
         <is>
           <t>Logs de depuración en el plan Basic Logs y muestreo en App Insights (~40%)</t>
         </is>
@@ -7323,7 +7790,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>SUMIF(Azure!$A$4:$A$53,"Ambiente Dev/Test",Azure!$I$4:$I$53)</f>
+        <f>SUMIF(Azure!$A$4:$A$53,"Ambiente Dev/Test",Azure!$J$4:$J$53)</f>
         <v/>
       </c>
       <c r="C9" s="5">
@@ -7334,7 +7801,7 @@
         <f>B9*(1-0.55)</f>
         <v/>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>Apagado automático noches y fines de semana + precios Dev/Test</t>
         </is>
@@ -7347,7 +7814,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>Azure!$I$54-SUM(B5:B9)</f>
+        <f>Azure!$J$54-SUM(B5:B9)</f>
         <v/>
       </c>
       <c r="C10" s="5">
@@ -7358,7 +7825,7 @@
         <f>B10</f>
         <v/>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="40" t="inlineStr">
         <is>
           <t>Servicios de consumo: se optimizan con autoescalado y cuotas</t>
         </is>
@@ -7406,19 +7873,19 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>Ahorro frente a pago por uso</t>
         </is>
       </c>
-      <c r="B16" s="39" t="n">
+      <c r="B16" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="42">
         <f>1-C14/B14</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="42">
         <f>1-D14/B14</f>
         <v/>
       </c>
@@ -7554,203 +8021,203 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Costo total y opciones de ahorro</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
+      <c r="B5" s="43" t="n">
         <v>0.2</v>
       </c>
-      <c r="C5" s="41" t="n">
+      <c r="C5" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="41" t="n">
+      <c r="D5" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="45">
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="45">
         <f>B5*D5</f>
         <v/>
       </c>
-      <c r="G5" s="37" t="inlineStr">
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>AWS es más barato en lista (API Gateway, mensajería y logs). Azure reduce la brecha con reservas y planes de ahorro.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Integración con el sistema de seguridad centralizado</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
+      <c r="B6" s="43" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="45">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="45">
         <f>B6*D6</f>
         <v/>
       </c>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>Entra ID se federa de forma nativa vía OIDC/SAML con el directorio corporativo, Acceso Condicional y MFA. En AWS se requiere Cognito como intermediario.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Seguridad y cumplimiento normativo (salud)</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="43" t="n">
         <v>0.2</v>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="41" t="n">
+      <c r="D7" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="45">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="45">
         <f>B7*D7</f>
         <v/>
       </c>
-      <c r="G7" s="37" t="inlineStr">
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>Ambos firman BAA de HIPAA y tienen ISO 27001, SOC 2 y HITRUST. Azure suma Defender for Cloud y Purview para datos clínicos.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>Servicios de salud e IA</t>
         </is>
       </c>
-      <c r="B8" s="40" t="n">
+      <c r="B8" s="43" t="n">
         <v>0.15</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="45">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="45">
         <f>B8*D8</f>
         <v/>
       </c>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>Azure Health Data Services (FHIR) + Azure OpenAI con red privada. AWS ofrece HealthLake y Bedrock, con menos opciones de modelos en red privada regional.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Escalabilidad y alta disponibilidad</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="43" t="n">
         <v>0.1</v>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="45">
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="45">
         <f>B9*D9</f>
         <v/>
       </c>
-      <c r="G9" s="37" t="inlineStr">
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>Zonas de disponibilidad, Kubernetes administrado y balanceo global en ambos.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>Compatibilidad con las tecnologías elegidas</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="43" t="n">
         <v>0.1</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="45">
         <f>B10*C10</f>
         <v/>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="45">
         <f>B10*D10</f>
         <v/>
       </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>React, Electron, Node.js, Python y GitHub Actions tienen integración de primera clase con Azure (GitHub y Azure son de Microsoft).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>Servicios adicionales y ecosistema</t>
         </is>
       </c>
-      <c r="B11" s="40" t="n">
+      <c r="B11" s="43" t="n">
         <v>0.05</v>
       </c>
-      <c r="C11" s="41" t="n">
+      <c r="C11" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="41" t="n">
+      <c r="D11" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="45">
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="45">
         <f>B11*D11</f>
         <v/>
       </c>
-      <c r="G11" s="37" t="inlineStr">
+      <c r="G11" s="40" t="inlineStr">
         <is>
           <t>Integración con Microsoft 365 y Teams para la comunicación con centros médicos, Power BI para indicadores del call center.</t>
         </is>
@@ -7762,17 +8229,17 @@
           <t>PUNTAJE TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="46">
         <f>SUM(B5:B11)</f>
         <v/>
       </c>
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
-      <c r="E12" s="44">
+      <c r="E12" s="47">
         <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="47">
         <f>SUM(F5:F11)</f>
         <v/>
       </c>
@@ -7794,19 +8261,19 @@
           <t>Necesidad</t>
         </is>
       </c>
-      <c r="B16" s="45" t="n"/>
+      <c r="B16" s="48" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Azure</t>
         </is>
       </c>
-      <c r="D16" s="45" t="n"/>
+      <c r="D16" s="48" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
-      <c r="F16" s="45" t="n"/>
+      <c r="F16" s="48" t="n"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Observación</t>
@@ -7819,19 +8286,19 @@
           <t>Identidad federada OIDC</t>
         </is>
       </c>
-      <c r="B17" s="45" t="n"/>
+      <c r="B17" s="48" t="n"/>
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Microsoft Entra ID</t>
         </is>
       </c>
-      <c r="D17" s="45" t="n"/>
+      <c r="D17" s="48" t="n"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Amazon Cognito</t>
         </is>
       </c>
-      <c r="F17" s="45" t="n"/>
+      <c r="F17" s="48" t="n"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Entra ID se conecta directo al directorio corporativo</t>
@@ -7844,19 +8311,19 @@
           <t>Entrada global, WAF y failover</t>
         </is>
       </c>
-      <c r="B18" s="45" t="n"/>
+      <c r="B18" s="48" t="n"/>
       <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Front Door Premium + WAF</t>
         </is>
       </c>
-      <c r="D18" s="45" t="n"/>
+      <c r="D18" s="48" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t>CloudFront + WAF + Route 53</t>
         </is>
       </c>
-      <c r="F18" s="45" t="n"/>
+      <c r="F18" s="48" t="n"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>En Azure un solo servicio cubre CDN, WAF y failover</t>
@@ -7869,19 +8336,19 @@
           <t>API Gateway</t>
         </is>
       </c>
-      <c r="B19" s="45" t="n"/>
+      <c r="B19" s="48" t="n"/>
       <c r="C19" s="4" t="inlineStr">
         <is>
           <t>API Management Standard v2</t>
         </is>
       </c>
-      <c r="D19" s="45" t="n"/>
+      <c r="D19" s="48" t="n"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>API Gateway HTTP API</t>
         </is>
       </c>
-      <c r="F19" s="45" t="n"/>
+      <c r="F19" s="48" t="n"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>APIM incluye portal de desarrolladores y políticas</t>
@@ -7894,19 +8361,19 @@
           <t>Kubernetes administrado</t>
         </is>
       </c>
-      <c r="B20" s="45" t="n"/>
+      <c r="B20" s="48" t="n"/>
       <c r="C20" s="4" t="inlineStr">
         <is>
           <t>AKS</t>
         </is>
       </c>
-      <c r="D20" s="45" t="n"/>
+      <c r="D20" s="48" t="n"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
           <t>EKS</t>
         </is>
       </c>
-      <c r="F20" s="45" t="n"/>
+      <c r="F20" s="48" t="n"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Mismo modelo de costo del plano de control</t>
@@ -7919,19 +8386,19 @@
           <t>Base de datos relacional</t>
         </is>
       </c>
-      <c r="B21" s="45" t="n"/>
+      <c r="B21" s="48" t="n"/>
       <c r="C21" s="4" t="inlineStr">
         <is>
           <t>PostgreSQL Flexible Server</t>
         </is>
       </c>
-      <c r="D21" s="45" t="n"/>
+      <c r="D21" s="48" t="n"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
           <t>RDS for PostgreSQL</t>
         </is>
       </c>
-      <c r="F21" s="45" t="n"/>
+      <c r="F21" s="48" t="n"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Ambos con HA en zonas y réplicas entre regiones</t>
@@ -7944,19 +8411,19 @@
           <t>Caché</t>
         </is>
       </c>
-      <c r="B22" s="45" t="n"/>
+      <c r="B22" s="48" t="n"/>
       <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Azure Cache for Redis</t>
         </is>
       </c>
-      <c r="D22" s="45" t="n"/>
+      <c r="D22" s="48" t="n"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>ElastiCache (Valkey)</t>
         </is>
       </c>
-      <c r="F22" s="45" t="n"/>
+      <c r="F22" s="48" t="n"/>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
@@ -7965,19 +8432,19 @@
           <t>Repositorio clínico FHIR</t>
         </is>
       </c>
-      <c r="B23" s="45" t="n"/>
+      <c r="B23" s="48" t="n"/>
       <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Azure Health Data Services</t>
         </is>
       </c>
-      <c r="D23" s="45" t="n"/>
+      <c r="D23" s="48" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>AWS HealthLake</t>
         </is>
       </c>
-      <c r="F23" s="45" t="n"/>
+      <c r="F23" s="48" t="n"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Azure cobra por uso; HealthLake cobra por hora del almacén</t>
@@ -7990,19 +8457,19 @@
           <t>Apoyo al diagnóstico</t>
         </is>
       </c>
-      <c r="B24" s="45" t="n"/>
+      <c r="B24" s="48" t="n"/>
       <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Azure OpenAI (gpt-4.1-mini)</t>
         </is>
       </c>
-      <c r="D24" s="45" t="n"/>
+      <c r="D24" s="48" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Amazon Bedrock (Nova Pro)</t>
         </is>
       </c>
-      <c r="F24" s="45" t="n"/>
+      <c r="F24" s="48" t="n"/>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Ambos sin entrenar con datos del cliente</t>
@@ -8015,19 +8482,19 @@
           <t>Mapas y rutas</t>
         </is>
       </c>
-      <c r="B25" s="45" t="n"/>
+      <c r="B25" s="48" t="n"/>
       <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Azure Maps</t>
         </is>
       </c>
-      <c r="D25" s="45" t="n"/>
+      <c r="D25" s="48" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Amazon Location Service</t>
         </is>
       </c>
-      <c r="F25" s="45" t="n"/>
+      <c r="F25" s="48" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>AWS es más barato por transacción</t>
@@ -8040,19 +8507,19 @@
           <t>Notificaciones</t>
         </is>
       </c>
-      <c r="B26" s="45" t="n"/>
+      <c r="B26" s="48" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="D26" s="45" t="n"/>
+      <c r="D26" s="48" t="n"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>End User Messaging + Connect + SES</t>
         </is>
       </c>
-      <c r="F26" s="45" t="n"/>
+      <c r="F26" s="48" t="n"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Azure unifica voz, SMS y correo en un servicio</t>
@@ -8065,19 +8532,19 @@
           <t>Mensajería</t>
         </is>
       </c>
-      <c r="B27" s="45" t="n"/>
+      <c r="B27" s="48" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Service Bus Premium</t>
         </is>
       </c>
-      <c r="D27" s="45" t="n"/>
+      <c r="D27" s="48" t="n"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
           <t>SQS + SNS</t>
         </is>
       </c>
-      <c r="F27" s="45" t="n"/>
+      <c r="F27" s="48" t="n"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Service Bus Premium da red privada y aislamiento</t>
@@ -8090,19 +8557,19 @@
           <t>Monitoreo</t>
         </is>
       </c>
-      <c r="B28" s="45" t="n"/>
+      <c r="B28" s="48" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Azure Monitor + Grafana</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n"/>
+      <c r="D28" s="48" t="n"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
           <t>CloudWatch + Managed Grafana</t>
         </is>
       </c>
-      <c r="F28" s="45" t="n"/>
+      <c r="F28" s="48" t="n"/>
       <c r="G28" s="4" t="inlineStr"/>
     </row>
   </sheetData>
@@ -8196,7 +8663,7 @@
           <t>Calculadora de precios de Azure</t>
         </is>
       </c>
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/calculator/</t>
         </is>
@@ -8208,7 +8675,7 @@
           <t>API oficial de precios minoristas de Azure</t>
         </is>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>https://prices.azure.com/api/retail/prices</t>
         </is>
@@ -8220,7 +8687,7 @@
           <t>Azure Reservations (descuentos por reserva)</t>
         </is>
       </c>
-      <c r="B6" s="46" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/cost-management-billing/reservations/save-compute-costs-reservations</t>
         </is>
@@ -8232,7 +8699,7 @@
           <t>Azure Savings Plan for Compute</t>
         </is>
       </c>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/offers/savings-plan-compute/</t>
         </is>
@@ -8244,7 +8711,7 @@
           <t>Calculadora de precios de AWS</t>
         </is>
       </c>
-      <c r="B8" s="46" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>https://calculator.aws/</t>
         </is>
@@ -8256,7 +8723,7 @@
           <t>AWS Price List (archivos oficiales de precios)</t>
         </is>
       </c>
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="49" t="inlineStr">
         <is>
           <t>https://pricing.us-east-1.amazonaws.com/offers/v1.0/aws/index.json</t>
         </is>
@@ -8268,7 +8735,7 @@
           <t>AWS Savings Plans</t>
         </is>
       </c>
-      <c r="B10" s="46" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/savingsplans/compute-pricing/</t>
         </is>
@@ -8280,7 +8747,7 @@
           <t>Calculadora de precios de Google Cloud</t>
         </is>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>https://cloud.google.com/products/calculator</t>
         </is>
@@ -8292,7 +8759,7 @@
           <t>Cumplimiento HIPAA en Azure</t>
         </is>
       </c>
-      <c r="B12" s="46" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/compliance/offerings/offering-hipaa-us</t>
         </is>
@@ -8304,14 +8771,14 @@
           <t>Cumplimiento HIPAA en AWS</t>
         </is>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/compliance/hipaa-compliance/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="inlineStr">
+      <c r="A15" s="50" t="inlineStr">
         <is>
           <t>Páginas de precios por servicio</t>
         </is>
@@ -8323,7 +8790,7 @@
           <t>Azure - Azure Kubernetes Service</t>
         </is>
       </c>
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/kubernetes-service/</t>
         </is>
@@ -8335,7 +8802,7 @@
           <t>Azure - AKS - nodos región primaria</t>
         </is>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/virtual-machines/linux/</t>
         </is>
@@ -8347,7 +8814,7 @@
           <t>Azure - Discos de SO de los nodos</t>
         </is>
       </c>
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/managed-disks/</t>
         </is>
@@ -8359,7 +8826,7 @@
           <t>Azure - Azure Container Registry</t>
         </is>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/container-registry/</t>
         </is>
@@ -8371,7 +8838,7 @@
           <t>Azure - PostgreSQL Flexible Server</t>
         </is>
       </c>
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/postgresql/flexible-server/</t>
         </is>
@@ -8383,7 +8850,7 @@
           <t>Azure - PostgreSQL - réplica geográfica</t>
         </is>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/postgresql/flexible-server/concepts-read-replicas</t>
         </is>
@@ -8395,7 +8862,7 @@
           <t>Azure - Azure Cache for Redis</t>
         </is>
       </c>
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/cache/</t>
         </is>
@@ -8407,7 +8874,7 @@
           <t>Azure - Blob Storage</t>
         </is>
       </c>
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/storage/blobs/</t>
         </is>
@@ -8419,7 +8886,7 @@
           <t>Azure - Health Data Services - FHIR</t>
         </is>
       </c>
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/health-data-services/</t>
         </is>
@@ -8431,7 +8898,7 @@
           <t>Azure - Azure Front Door</t>
         </is>
       </c>
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/frontdoor/</t>
         </is>
@@ -8443,7 +8910,7 @@
           <t>Azure - API Management</t>
         </is>
       </c>
-      <c r="B26" s="46" t="inlineStr">
+      <c r="B26" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/api-management/</t>
         </is>
@@ -8455,7 +8922,7 @@
           <t>Azure - Private Endpoints</t>
         </is>
       </c>
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/private-link/</t>
         </is>
@@ -8467,7 +8934,7 @@
           <t>Azure - Transferencia entre regiones</t>
         </is>
       </c>
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/bandwidth/</t>
         </is>
@@ -8479,7 +8946,7 @@
           <t>Azure - Azure DNS</t>
         </is>
       </c>
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/dns/</t>
         </is>
@@ -8491,7 +8958,7 @@
           <t>Azure - Microsoft Entra ID</t>
         </is>
       </c>
-      <c r="B30" s="46" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/es-es/security/business/microsoft-entra-pricing</t>
         </is>
@@ -8503,7 +8970,7 @@
           <t>Azure - Azure Key Vault</t>
         </is>
       </c>
-      <c r="B31" s="46" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/key-vault/</t>
         </is>
@@ -8515,7 +8982,7 @@
           <t>Azure - Defender for Containers</t>
         </is>
       </c>
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/defender-for-cloud/</t>
         </is>
@@ -8527,7 +8994,7 @@
           <t>Azure - Certificados TLS</t>
         </is>
       </c>
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/frontdoor/domain</t>
         </is>
@@ -8539,7 +9006,7 @@
           <t>Azure - Log Analytics + Application Insights</t>
         </is>
       </c>
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/monitor/</t>
         </is>
@@ -8551,7 +9018,7 @@
           <t>Azure - Azure Managed Grafana</t>
         </is>
       </c>
-      <c r="B35" s="46" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/managed-grafana/</t>
         </is>
@@ -8563,7 +9030,7 @@
           <t>Azure - Azure Service Bus</t>
         </is>
       </c>
-      <c r="B36" s="46" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/service-bus/</t>
         </is>
@@ -8575,7 +9042,7 @@
           <t>Azure - Azure OpenAI</t>
         </is>
       </c>
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/cognitive-services/openai-service/</t>
         </is>
@@ -8587,7 +9054,7 @@
           <t>Azure - Azure Maps</t>
         </is>
       </c>
-      <c r="B38" s="46" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/azure-maps/</t>
         </is>
@@ -8599,7 +9066,7 @@
           <t>Azure - Communication Services</t>
         </is>
       </c>
-      <c r="B39" s="46" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/communication-services/concepts/sms-pricing</t>
         </is>
@@ -8611,7 +9078,7 @@
           <t>Azure - Communication Services</t>
         </is>
       </c>
-      <c r="B40" s="46" t="inlineStr">
+      <c r="B40" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/communication-services/concepts/pricing</t>
         </is>
@@ -8623,7 +9090,7 @@
           <t>Azure - Communication Services</t>
         </is>
       </c>
-      <c r="B41" s="46" t="inlineStr">
+      <c r="B41" s="49" t="inlineStr">
         <is>
           <t>https://azure.microsoft.com/es-es/pricing/details/communication-services/</t>
         </is>
@@ -8635,7 +9102,7 @@
           <t>Azure - Communication Services</t>
         </is>
       </c>
-      <c r="B42" s="46" t="inlineStr">
+      <c r="B42" s="49" t="inlineStr">
         <is>
           <t>https://learn.microsoft.com/azure/communication-services/concepts/numbers/number-types</t>
         </is>
@@ -8647,7 +9114,7 @@
           <t>AWS - Amazon EKS</t>
         </is>
       </c>
-      <c r="B43" s="46" t="inlineStr">
+      <c r="B43" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/eks/pricing/</t>
         </is>
@@ -8659,7 +9126,7 @@
           <t>AWS - EKS - nodos región primaria</t>
         </is>
       </c>
-      <c r="B44" s="46" t="inlineStr">
+      <c r="B44" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ec2/pricing/on-demand/</t>
         </is>
@@ -8671,7 +9138,7 @@
           <t>AWS - EBS de los nodos</t>
         </is>
       </c>
-      <c r="B45" s="46" t="inlineStr">
+      <c r="B45" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ebs/pricing/</t>
         </is>
@@ -8683,7 +9150,7 @@
           <t>AWS - Amazon ECR</t>
         </is>
       </c>
-      <c r="B46" s="46" t="inlineStr">
+      <c r="B46" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ecr/pricing/</t>
         </is>
@@ -8695,7 +9162,7 @@
           <t>AWS - RDS for PostgreSQL</t>
         </is>
       </c>
-      <c r="B47" s="46" t="inlineStr">
+      <c r="B47" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/rds/postgresql/pricing/</t>
         </is>
@@ -8707,7 +9174,7 @@
           <t>AWS - ElastiCache</t>
         </is>
       </c>
-      <c r="B48" s="46" t="inlineStr">
+      <c r="B48" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/elasticache/pricing/</t>
         </is>
@@ -8719,7 +9186,7 @@
           <t>AWS - Amazon S3</t>
         </is>
       </c>
-      <c r="B49" s="46" t="inlineStr">
+      <c r="B49" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/s3/pricing/</t>
         </is>
@@ -8731,7 +9198,7 @@
           <t>AWS - AWS HealthLake</t>
         </is>
       </c>
-      <c r="B50" s="46" t="inlineStr">
+      <c r="B50" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/healthlake/pricing/</t>
         </is>
@@ -8743,7 +9210,7 @@
           <t>AWS - Amazon CloudFront</t>
         </is>
       </c>
-      <c r="B51" s="46" t="inlineStr">
+      <c r="B51" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudfront/pricing/</t>
         </is>
@@ -8755,7 +9222,7 @@
           <t>AWS - Amazon API Gateway</t>
         </is>
       </c>
-      <c r="B52" s="46" t="inlineStr">
+      <c r="B52" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/api-gateway/pricing/</t>
         </is>
@@ -8767,7 +9234,7 @@
           <t>AWS - Application Load Balancer</t>
         </is>
       </c>
-      <c r="B53" s="46" t="inlineStr">
+      <c r="B53" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/elasticloadbalancing/pricing/</t>
         </is>
@@ -8779,7 +9246,7 @@
           <t>AWS - NAT Gateway</t>
         </is>
       </c>
-      <c r="B54" s="46" t="inlineStr">
+      <c r="B54" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/vpc/pricing/</t>
         </is>
@@ -8791,7 +9258,7 @@
           <t>AWS - VPC Interface Endpoints (PrivateLink)</t>
         </is>
       </c>
-      <c r="B55" s="46" t="inlineStr">
+      <c r="B55" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/privatelink/pricing/</t>
         </is>
@@ -8803,7 +9270,7 @@
           <t>AWS - Transferencia entre regiones</t>
         </is>
       </c>
-      <c r="B56" s="46" t="inlineStr">
+      <c r="B56" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ec2/pricing/on-demand/#Data_Transfer</t>
         </is>
@@ -8815,7 +9282,7 @@
           <t>AWS - Amazon Route 53</t>
         </is>
       </c>
-      <c r="B57" s="46" t="inlineStr">
+      <c r="B57" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/route53/pricing/</t>
         </is>
@@ -8827,7 +9294,7 @@
           <t>AWS - Amazon Cognito</t>
         </is>
       </c>
-      <c r="B58" s="46" t="inlineStr">
+      <c r="B58" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cognito/pricing/</t>
         </is>
@@ -8839,7 +9306,7 @@
           <t>AWS - AWS WAF</t>
         </is>
       </c>
-      <c r="B59" s="46" t="inlineStr">
+      <c r="B59" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/waf/pricing/</t>
         </is>
@@ -8851,7 +9318,7 @@
           <t>AWS - AWS Secrets Manager + KMS</t>
         </is>
       </c>
-      <c r="B60" s="46" t="inlineStr">
+      <c r="B60" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/secrets-manager/pricing/</t>
         </is>
@@ -8863,7 +9330,7 @@
           <t>AWS - Amazon GuardDuty</t>
         </is>
       </c>
-      <c r="B61" s="46" t="inlineStr">
+      <c r="B61" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/guardduty/pricing/</t>
         </is>
@@ -8875,7 +9342,7 @@
           <t>AWS - AWS Security Hub</t>
         </is>
       </c>
-      <c r="B62" s="46" t="inlineStr">
+      <c r="B62" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/security-hub/pricing/</t>
         </is>
@@ -8887,7 +9354,7 @@
           <t>AWS - AWS Certificate Manager</t>
         </is>
       </c>
-      <c r="B63" s="46" t="inlineStr">
+      <c r="B63" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/certificate-manager/pricing/</t>
         </is>
@@ -8899,7 +9366,7 @@
           <t>AWS - CloudWatch Logs</t>
         </is>
       </c>
-      <c r="B64" s="46" t="inlineStr">
+      <c r="B64" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/cloudwatch/pricing/</t>
         </is>
@@ -8911,7 +9378,7 @@
           <t>AWS - Amazon Managed Service for Prometheus</t>
         </is>
       </c>
-      <c r="B65" s="46" t="inlineStr">
+      <c r="B65" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/prometheus/pricing/</t>
         </is>
@@ -8923,7 +9390,7 @@
           <t>AWS - Amazon Managed Grafana</t>
         </is>
       </c>
-      <c r="B66" s="46" t="inlineStr">
+      <c r="B66" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/grafana/pricing/</t>
         </is>
@@ -8935,7 +9402,7 @@
           <t>AWS - AWS X-Ray</t>
         </is>
       </c>
-      <c r="B67" s="46" t="inlineStr">
+      <c r="B67" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/xray/pricing/</t>
         </is>
@@ -8947,7 +9414,7 @@
           <t>AWS - Amazon SQS + SNS</t>
         </is>
       </c>
-      <c r="B68" s="46" t="inlineStr">
+      <c r="B68" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/sqs/pricing/</t>
         </is>
@@ -8959,7 +9426,7 @@
           <t>AWS - Amazon Bedrock</t>
         </is>
       </c>
-      <c r="B69" s="46" t="inlineStr">
+      <c r="B69" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/bedrock/pricing/</t>
         </is>
@@ -8971,7 +9438,7 @@
           <t>AWS - Amazon Location Service</t>
         </is>
       </c>
-      <c r="B70" s="46" t="inlineStr">
+      <c r="B70" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/location/pricing/</t>
         </is>
@@ -8983,7 +9450,7 @@
           <t>AWS - AWS End User Messaging SMS</t>
         </is>
       </c>
-      <c r="B71" s="46" t="inlineStr">
+      <c r="B71" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/end-user-messaging/pricing/</t>
         </is>
@@ -8995,7 +9462,7 @@
           <t>AWS - Amazon Connect</t>
         </is>
       </c>
-      <c r="B72" s="46" t="inlineStr">
+      <c r="B72" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/connect/pricing/</t>
         </is>
@@ -9007,7 +9474,7 @@
           <t>AWS - Amazon SES</t>
         </is>
       </c>
-      <c r="B73" s="46" t="inlineStr">
+      <c r="B73" s="49" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/ses/pricing/</t>
         </is>
